--- a/Result/profitability/6585.xlsx
+++ b/Result/profitability/6585.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM37"/>
+  <dimension ref="A1:AM38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5129,6 +5129,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>6585</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>930</v>
+      </c>
+      <c r="D38" t="n">
+        <v>564</v>
+      </c>
+      <c r="E38" t="n">
+        <v>366</v>
+      </c>
+      <c r="F38" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="G38" t="n">
+        <v>266</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>28.61%</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>6</v>
+      </c>
+      <c r="J38" t="n">
+        <v>272</v>
+      </c>
+      <c r="K38" t="n">
+        <v>212</v>
+      </c>
+      <c r="L38" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.8775</v>
+      </c>
+      <c r="N38" t="n">
+        <v>34.88125</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
+      </c>
+      <c r="V38" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.5806451612903225</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>4.649999999999999</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0.1340830449826989</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>8.379999999999999</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.2707592891760904</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK38" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
